--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -577,7 +577,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>10500</x:v>
+        <x:v>11055.233768</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.5</x:v>
+        <x:v>4.737112</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>900</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -577,7 +577,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>11055.233768</x:v>
+        <x:v>12350</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.737112</x:v>
+        <x:v>4.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>535</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -577,7 +577,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>12350</x:v>
+        <x:v>10731.54221</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.8</x:v>
+        <x:v>6.55</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>545</x:v>
+        <x:v>554.2409638554217</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -577,7 +577,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>10731.54221</x:v>
+        <x:v>12470</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>6.55</x:v>
+        <x:v>4.92</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>554.2409638554217</x:v>
+        <x:v>560</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">

--- a/submission/DE-FY2026Q3.xlsx
+++ b/submission/DE-FY2026Q3.xlsx
@@ -577,7 +577,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C7" s="34">
-        <x:v>12470</x:v>
+        <x:v>11850</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="29" customHeight="1">
@@ -588,7 +588,7 @@
         <x:v>USD / share</x:v>
       </x:c>
       <x:c r="C8" s="35">
-        <x:v>4.92</x:v>
+        <x:v>4.8</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="29" customHeight="1">
@@ -599,7 +599,7 @@
         <x:v>USDm</x:v>
       </x:c>
       <x:c r="C9" s="34">
-        <x:v>560</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
